--- a/artfynd/A 14834-2023 artfynd.xlsx
+++ b/artfynd/A 14834-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3680,6 +3680,130 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>109927454</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57126</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Accipiter gentilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Slätten väster om Sunnersbol 68 m SW, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>662897</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6654107</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-06-09</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>05:04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-06-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14834-2023 artfynd.xlsx
+++ b/artfynd/A 14834-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14834-2023 artfynd.xlsx
+++ b/artfynd/A 14834-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3804,6 +3804,126 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>109927457</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57245</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Slätten väster om Sunnersbol 68 m SW, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>662897</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6654107</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stavby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-06-09</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>05:04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-06-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14834-2023 artfynd.xlsx
+++ b/artfynd/A 14834-2023 artfynd.xlsx
@@ -923,7 +923,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">

--- a/artfynd/A 14834-2023 artfynd.xlsx
+++ b/artfynd/A 14834-2023 artfynd.xlsx
@@ -3553,7 +3553,7 @@
         <v>109927444</v>
       </c>
       <c r="B27" t="n">
-        <v>56577</v>
+        <v>56681</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 14834-2023 artfynd.xlsx
+++ b/artfynd/A 14834-2023 artfynd.xlsx
@@ -3553,7 +3553,7 @@
         <v>109927444</v>
       </c>
       <c r="B27" t="n">
-        <v>56681</v>
+        <v>56683</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 14834-2023 artfynd.xlsx
+++ b/artfynd/A 14834-2023 artfynd.xlsx
@@ -3553,7 +3553,7 @@
         <v>109927444</v>
       </c>
       <c r="B27" t="n">
-        <v>56683</v>
+        <v>56688</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 14834-2023 artfynd.xlsx
+++ b/artfynd/A 14834-2023 artfynd.xlsx
@@ -3568,11 +3568,6 @@
       <c r="E27" t="n">
         <v>100038</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Skogsduva</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>Columba oenas</t>

--- a/artfynd/A 14834-2023 artfynd.xlsx
+++ b/artfynd/A 14834-2023 artfynd.xlsx
@@ -3553,7 +3553,7 @@
         <v>109927444</v>
       </c>
       <c r="B27" t="n">
-        <v>56688</v>
+        <v>56692</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3567,6 +3567,11 @@
       </c>
       <c r="E27" t="n">
         <v>100038</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>

--- a/artfynd/A 14834-2023 artfynd.xlsx
+++ b/artfynd/A 14834-2023 artfynd.xlsx
@@ -3553,7 +3553,7 @@
         <v>109927444</v>
       </c>
       <c r="B27" t="n">
-        <v>56692</v>
+        <v>56693</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
